--- a/forms/trg/Formulir_TRG_afdays.xlsx
+++ b/forms/trg/Formulir_TRG_afdays.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
